--- a/output/pdf_financials_xlsx/ELXR.H.xlsx
+++ b/output/pdf_financials_xlsx/ELXR.H.xlsx
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.24442</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.12221</v>
+        <v>-0.12221</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.144684</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.12221</v>
+        <v>-0.12221</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.144684</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>8.320958452401134</v>
+        <v>-8.320958452401134</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>-13.74101915122966</v>
@@ -5632,13 +5632,13 @@
         <v>17.432018</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>17.432018</v>
+        <v>21.407765</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>17.432018</v>
+        <v>21.407765</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>17.692546</v>
+        <v>21.407765</v>
       </c>
     </row>
     <row r="93">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.12221</v>
+        <v>-0.12221</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.144684</v>
@@ -9512,7 +9512,11 @@
           <t>Warrants reserve 9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10499,7 +10503,11 @@
           <t>Warrants reserve 10</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -43142,7 +43150,7 @@
         </is>
       </c>
       <c r="G391" s="5" t="n">
-        <v>0.12221</v>
+        <v>-0.12221</v>
       </c>
       <c r="H391" s="5" t="n">
         <v>-0.144684</v>

--- a/output/pdf_financials_xlsx/ELXR.H.xlsx
+++ b/output/pdf_financials_xlsx/ELXR.H.xlsx
@@ -2514,25 +2514,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.005799</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.02396</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.011723</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.572825</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.486137</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.01857</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>6.566218</v>
@@ -2541,22 +2541,22 @@
         <v>0.924502</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.102748</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.301763</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.065425</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.020301</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.020301</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.035122</v>
       </c>
     </row>
     <row r="35">
@@ -2618,25 +2618,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.005799</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.02396</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.011723</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>6.572825</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.486137</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.01857</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>6.566218</v>
@@ -2645,22 +2645,22 @@
         <v>0.924502</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.102748</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.301763</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.065425</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.020301</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.020301</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.035122</v>
       </c>
     </row>
     <row r="37">
@@ -3242,25 +3242,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.08412</v>
+        <v>0.078321</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.214021</v>
+        <v>0.190061</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.134384</v>
+        <v>0.122661</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>8.172598000000001</v>
+        <v>1.599773</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7.739021</v>
+        <v>7.252884</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.695811</v>
+        <v>0.677241</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -3269,22 +3269,22 @@
         <v>0.717103</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.102748</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>13.585926</v>
+        <v>13.284163</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.525952</v>
+        <v>2.460527</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.020301</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.020301</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.049122</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="49">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">

--- a/output/pdf_financials_xlsx/ELXR.H.xlsx
+++ b/output/pdf_financials_xlsx/ELXR.H.xlsx
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.018738</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.013961</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.12221</v>
+        <v>0.140948</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.144684</v>
+        <v>-0.130723</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.108301</v>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>8.320958452401134</v>
+        <v>9.596779739375135</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-13.74101915122966</v>
+        <v>-12.41510634559588</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.018738</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.013961</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -43227,7 +43227,11 @@
           <t>Depreciation ‐ Property and equipment</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
